--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/130.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/130.xlsx
@@ -426,13 +426,13 @@
         <v>-19.04025066206849</v>
       </c>
       <c r="E2">
-        <v>-17.7860411177077</v>
+        <v>-27.01604929572555</v>
       </c>
       <c r="F2">
-        <v>-1.703396060278812</v>
+        <v>-4.870911476940575</v>
       </c>
       <c r="G2">
-        <v>-14.84082127364753</v>
+        <v>-19.74864279675577</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.74614834562637</v>
       </c>
       <c r="E3">
-        <v>-19.17803968597748</v>
+        <v>-27.24675693252032</v>
       </c>
       <c r="F3">
-        <v>-1.751406578210266</v>
+        <v>-4.698271426523131</v>
       </c>
       <c r="G3">
-        <v>-14.44548821589017</v>
+        <v>-18.64014607671779</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.41728289717234</v>
       </c>
       <c r="E4">
-        <v>-19.51442832068926</v>
+        <v>-27.40699698528174</v>
       </c>
       <c r="F4">
-        <v>-1.585948473175093</v>
+        <v>-4.799125157813971</v>
       </c>
       <c r="G4">
-        <v>-14.68812962837877</v>
+        <v>-19.23896408948411</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.07382642332371</v>
       </c>
       <c r="E5">
-        <v>-19.84263853134318</v>
+        <v>-28.14328157418887</v>
       </c>
       <c r="F5">
-        <v>-1.546004597012101</v>
+        <v>-4.988025231980967</v>
       </c>
       <c r="G5">
-        <v>-13.92763762632471</v>
+        <v>-18.52632214143143</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.72099610847446</v>
       </c>
       <c r="E6">
-        <v>-21.12533785096383</v>
+        <v>-29.41142184987485</v>
       </c>
       <c r="F6">
-        <v>-1.475426037558777</v>
+        <v>-4.609086078468125</v>
       </c>
       <c r="G6">
-        <v>-13.3398215494472</v>
+        <v>-18.56050590763772</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.36213175642193</v>
       </c>
       <c r="E7">
-        <v>-21.01807641561815</v>
+        <v>-31.10696403087877</v>
       </c>
       <c r="F7">
-        <v>-1.42372762795006</v>
+        <v>-4.75917879654877</v>
       </c>
       <c r="G7">
-        <v>-13.33768219299045</v>
+        <v>-17.99950725456556</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.00665204019957</v>
       </c>
       <c r="E8">
-        <v>-21.54475152813223</v>
+        <v>-30.46666724127523</v>
       </c>
       <c r="F8">
-        <v>-1.349048649852879</v>
+        <v>-4.657564623982161</v>
       </c>
       <c r="G8">
-        <v>-13.2905408828459</v>
+        <v>-18.23644426337307</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.6617323063064</v>
       </c>
       <c r="E9">
-        <v>-22.33689937239798</v>
+        <v>-30.08624146107586</v>
       </c>
       <c r="F9">
-        <v>-1.452871249915352</v>
+        <v>-4.566781355207154</v>
       </c>
       <c r="G9">
-        <v>-12.25938419557481</v>
+        <v>-18.38809904262904</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.32258683337071</v>
       </c>
       <c r="E10">
-        <v>-23.06285904056761</v>
+        <v>-31.06095020648683</v>
       </c>
       <c r="F10">
-        <v>-1.287553967338655</v>
+        <v>-4.758614678347464</v>
       </c>
       <c r="G10">
-        <v>-11.98714452400924</v>
+        <v>-17.46338354213555</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.99612300141279</v>
       </c>
       <c r="E11">
-        <v>-23.81892400394024</v>
+        <v>-31.78092776049233</v>
       </c>
       <c r="F11">
-        <v>-1.140885720101183</v>
+        <v>-4.384466801892414</v>
       </c>
       <c r="G11">
-        <v>-11.84902150246442</v>
+        <v>-17.46959981637992</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.68474507310339</v>
       </c>
       <c r="E12">
-        <v>-24.1083070784524</v>
+        <v>-32.91741397559032</v>
       </c>
       <c r="F12">
-        <v>-1.206179295524646</v>
+        <v>-4.838631655988284</v>
       </c>
       <c r="G12">
-        <v>-11.47189102130808</v>
+        <v>-18.03470163701217</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.3849651689703</v>
       </c>
       <c r="E13">
-        <v>-25.09882925509815</v>
+        <v>-33.01339045370889</v>
       </c>
       <c r="F13">
-        <v>-1.120429187089049</v>
+        <v>-4.641372526359638</v>
       </c>
       <c r="G13">
-        <v>-10.6133003382913</v>
+        <v>-16.82149457456918</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.11131505457009</v>
       </c>
       <c r="E14">
-        <v>-25.88328775049887</v>
+        <v>-32.97158131743307</v>
       </c>
       <c r="F14">
-        <v>-0.901027796783572</v>
+        <v>-4.501528369786429</v>
       </c>
       <c r="G14">
-        <v>-10.58095405615829</v>
+        <v>-15.21075275470245</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.8613510528977</v>
       </c>
       <c r="E15">
-        <v>-26.57888852892108</v>
+        <v>-34.48137908006437</v>
       </c>
       <c r="F15">
-        <v>-0.8498943337435642</v>
+        <v>-3.8790989018947</v>
       </c>
       <c r="G15">
-        <v>-9.87269582010903</v>
+        <v>-16.22350999207896</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.63341539554242</v>
       </c>
       <c r="E16">
-        <v>-27.3087336277893</v>
+        <v>-35.33408620723469</v>
       </c>
       <c r="F16">
-        <v>-0.816362849645643</v>
+        <v>-4.206701642353848</v>
       </c>
       <c r="G16">
-        <v>-9.594799322574978</v>
+        <v>-15.37454641311759</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.42784475472093</v>
       </c>
       <c r="E17">
-        <v>-27.5607115069981</v>
+        <v>-35.10610244755554</v>
       </c>
       <c r="F17">
-        <v>-0.464009319558248</v>
+        <v>-4.029785559403153</v>
       </c>
       <c r="G17">
-        <v>-9.309585700963366</v>
+        <v>-15.34455604806426</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.23808912396575</v>
       </c>
       <c r="E18">
-        <v>-28.94277007482104</v>
+        <v>-36.13151425219338</v>
       </c>
       <c r="F18">
-        <v>-0.3882468368982052</v>
+        <v>-3.991181153330487</v>
       </c>
       <c r="G18">
-        <v>-8.96180574665626</v>
+        <v>-15.30554888616558</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.06060837380448</v>
       </c>
       <c r="E19">
-        <v>-29.72370088896979</v>
+        <v>-35.97461394901262</v>
       </c>
       <c r="F19">
-        <v>-0.2989844506747389</v>
+        <v>-4.022333566247568</v>
       </c>
       <c r="G19">
-        <v>-8.322548318780562</v>
+        <v>-14.57050275730502</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.89552821270766</v>
       </c>
       <c r="E20">
-        <v>-30.08052879111519</v>
+        <v>-37.28279272763743</v>
       </c>
       <c r="F20">
-        <v>-0.2315959340895963</v>
+        <v>-3.665985648543874</v>
       </c>
       <c r="G20">
-        <v>-7.967077181138119</v>
+        <v>-14.38217704590069</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.729915006607</v>
       </c>
       <c r="E21">
-        <v>-30.44438941339449</v>
+        <v>-37.79218944757525</v>
       </c>
       <c r="F21">
-        <v>-0.1327319413002809</v>
+        <v>-3.453926078529409</v>
       </c>
       <c r="G21">
-        <v>-7.857458131280191</v>
+        <v>-13.54655491380002</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.56242807509769</v>
       </c>
       <c r="E22">
-        <v>-30.86107015649927</v>
+        <v>-38.00509338880886</v>
       </c>
       <c r="F22">
-        <v>-0.09906046311128663</v>
+        <v>-3.927847495182048</v>
       </c>
       <c r="G22">
-        <v>-7.726051770267548</v>
+        <v>-13.38716301410687</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.39055959619095</v>
       </c>
       <c r="E23">
-        <v>-31.88928508654787</v>
+        <v>-39.11893044115749</v>
       </c>
       <c r="F23">
-        <v>0.07932928544898971</v>
+        <v>-3.283990647682104</v>
       </c>
       <c r="G23">
-        <v>-7.431526041870232</v>
+        <v>-13.89983255482997</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.20998524670061</v>
       </c>
       <c r="E24">
-        <v>-32.83338587614099</v>
+        <v>-38.57369084944896</v>
       </c>
       <c r="F24">
-        <v>0.1613020385278204</v>
+        <v>-3.497180939201391</v>
       </c>
       <c r="G24">
-        <v>-7.148651931230503</v>
+        <v>-13.7471179410103</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.02989748914708</v>
       </c>
       <c r="E25">
-        <v>-32.15199771339185</v>
+        <v>-39.18310571055719</v>
       </c>
       <c r="F25">
-        <v>0.3336107419841455</v>
+        <v>-3.17336218103823</v>
       </c>
       <c r="G25">
-        <v>-7.286751984224412</v>
+        <v>-13.39628809126369</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.85422999436834</v>
       </c>
       <c r="E26">
-        <v>-32.45543037851281</v>
+        <v>-39.95876764519801</v>
       </c>
       <c r="F26">
-        <v>0.1076196889893984</v>
+        <v>-3.242515948558739</v>
       </c>
       <c r="G26">
-        <v>-7.061161439569469</v>
+        <v>-13.00251197313629</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.68412182335462</v>
       </c>
       <c r="E27">
-        <v>-32.08403211124773</v>
+        <v>-38.52793061960145</v>
       </c>
       <c r="F27">
-        <v>0.5306205330245491</v>
+        <v>-3.313893054188361</v>
       </c>
       <c r="G27">
-        <v>-7.047928273020228</v>
+        <v>-13.64886996446663</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.5275675929489</v>
       </c>
       <c r="E28">
-        <v>-32.83560482840475</v>
+        <v>-39.63050535709299</v>
       </c>
       <c r="F28">
-        <v>0.3394060003341309</v>
+        <v>-3.023903164020727</v>
       </c>
       <c r="G28">
-        <v>-7.307817426636046</v>
+        <v>-13.84364327623526</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.3873365782046</v>
       </c>
       <c r="E29">
-        <v>-32.54649346233305</v>
+        <v>-39.0227071612055</v>
       </c>
       <c r="F29">
-        <v>0.1090701603117004</v>
+        <v>-3.392629375824454</v>
       </c>
       <c r="G29">
-        <v>-7.24492625300617</v>
+        <v>-14.5514421412662</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.26352124136801</v>
       </c>
       <c r="E30">
-        <v>-32.55742067011356</v>
+        <v>-38.62957448294061</v>
       </c>
       <c r="F30">
-        <v>0.1706377391573708</v>
+        <v>-3.327979441872966</v>
       </c>
       <c r="G30">
-        <v>-7.514081576305861</v>
+        <v>-14.08967583120555</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.16327538168691</v>
       </c>
       <c r="E31">
-        <v>-32.64618328913791</v>
+        <v>-39.25916595999002</v>
       </c>
       <c r="F31">
-        <v>0.2275035046247513</v>
+        <v>-3.094636628178374</v>
       </c>
       <c r="G31">
-        <v>-7.319360764082173</v>
+        <v>-14.17399666284016</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.08025469702884</v>
       </c>
       <c r="E32">
-        <v>-31.59296665409296</v>
+        <v>-38.61732722498687</v>
       </c>
       <c r="F32">
-        <v>0.3570361437679128</v>
+        <v>-3.10263948565682</v>
       </c>
       <c r="G32">
-        <v>-7.553049363545826</v>
+        <v>-13.53400096011358</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.0122816416724</v>
       </c>
       <c r="E33">
-        <v>-31.82774538902063</v>
+        <v>-39.19815609392168</v>
       </c>
       <c r="F33">
-        <v>0.1430837542380509</v>
+        <v>-3.302547734239619</v>
       </c>
       <c r="G33">
-        <v>-7.571588265356689</v>
+        <v>-14.19152658902149</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.95730331911066</v>
       </c>
       <c r="E34">
-        <v>-31.52779964888558</v>
+        <v>-37.72913950396645</v>
       </c>
       <c r="F34">
-        <v>0.1466018305977403</v>
+        <v>-3.651222484691181</v>
       </c>
       <c r="G34">
-        <v>-7.629272140371727</v>
+        <v>-14.78621026262291</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.90880974948199</v>
       </c>
       <c r="E35">
-        <v>-30.52374412766791</v>
+        <v>-37.67188827132448</v>
       </c>
       <c r="F35">
-        <v>0.2922114242944346</v>
+        <v>-3.645056117744741</v>
       </c>
       <c r="G35">
-        <v>-8.132207937338734</v>
+        <v>-14.64905848265968</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.866129960852</v>
       </c>
       <c r="E36">
-        <v>-30.41856126189175</v>
+        <v>-36.90532630520207</v>
       </c>
       <c r="F36">
-        <v>0.3495866357145368</v>
+        <v>-3.345396694884229</v>
       </c>
       <c r="G36">
-        <v>-8.039907174871555</v>
+        <v>-14.53054732237566</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.82811117634908</v>
       </c>
       <c r="E37">
-        <v>-30.20672377628694</v>
+        <v>-37.54209088507962</v>
       </c>
       <c r="F37">
-        <v>0.3273863893195101</v>
+        <v>-3.079211598770844</v>
       </c>
       <c r="G37">
-        <v>-7.969360911343493</v>
+        <v>-14.81688968420372</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.78589907827269</v>
       </c>
       <c r="E38">
-        <v>-29.86836299114482</v>
+        <v>-36.70941999115625</v>
       </c>
       <c r="F38">
-        <v>0.4122302638164438</v>
+        <v>-3.403927478831236</v>
       </c>
       <c r="G38">
-        <v>-8.140023807093332</v>
+        <v>-14.48912846263079</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.74172743023093</v>
       </c>
       <c r="E39">
-        <v>-28.89113641418558</v>
+        <v>-35.69873478399133</v>
       </c>
       <c r="F39">
-        <v>0.1281118417998526</v>
+        <v>-3.580811255453223</v>
       </c>
       <c r="G39">
-        <v>-8.511205433562397</v>
+        <v>-14.8110983281513</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.69574459996236</v>
       </c>
       <c r="E40">
-        <v>-28.51735164111847</v>
+        <v>-35.91746234279882</v>
       </c>
       <c r="F40">
-        <v>0.3270658111346266</v>
+        <v>-3.355113444519067</v>
       </c>
       <c r="G40">
-        <v>-8.541537045657904</v>
+        <v>-14.70410753676249</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.64566262576095</v>
       </c>
       <c r="E41">
-        <v>-28.38997925270472</v>
+        <v>-35.19149588191817</v>
       </c>
       <c r="F41">
-        <v>0.5594120988436516</v>
+        <v>-2.989871346011514</v>
       </c>
       <c r="G41">
-        <v>-8.38142327722168</v>
+        <v>-15.24852289607321</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.60114269490747</v>
       </c>
       <c r="E42">
-        <v>-27.26031518369929</v>
+        <v>-35.72839402450457</v>
       </c>
       <c r="F42">
-        <v>0.3380574182023733</v>
+        <v>-3.27094634619022</v>
       </c>
       <c r="G42">
-        <v>-8.476808387954737</v>
+        <v>-15.05917508415312</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.56242523625554</v>
       </c>
       <c r="E43">
-        <v>-26.90687684434863</v>
+        <v>-35.42511759173689</v>
       </c>
       <c r="F43">
-        <v>0.2876727992944962</v>
+        <v>-3.190460512599415</v>
       </c>
       <c r="G43">
-        <v>-9.27788581947757</v>
+        <v>-15.43514893470975</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.53057915957474</v>
       </c>
       <c r="E44">
-        <v>-26.55361058701027</v>
+        <v>-34.36114356668671</v>
       </c>
       <c r="F44">
-        <v>0.6550785934581609</v>
+        <v>-3.24347519801118</v>
       </c>
       <c r="G44">
-        <v>-9.122766070254821</v>
+        <v>-15.34967639430777</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.51122919509962</v>
       </c>
       <c r="E45">
-        <v>-25.69820901780539</v>
+        <v>-33.54835946636802</v>
       </c>
       <c r="F45">
-        <v>0.6507222092868383</v>
+        <v>-3.266454109764839</v>
       </c>
       <c r="G45">
-        <v>-8.926211055179404</v>
+        <v>-14.9704213221917</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.50561544533865</v>
       </c>
       <c r="E46">
-        <v>-25.04626725729112</v>
+        <v>-33.41620048092817</v>
       </c>
       <c r="F46">
-        <v>0.5666155817783961</v>
+        <v>-3.056595511939612</v>
       </c>
       <c r="G46">
-        <v>-8.758566883264255</v>
+        <v>-15.2362822990457</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.51636211805307</v>
       </c>
       <c r="E47">
-        <v>-24.784652785394</v>
+        <v>-33.87165628272362</v>
       </c>
       <c r="F47">
-        <v>0.5161365289865998</v>
+        <v>-3.269490904663502</v>
       </c>
       <c r="G47">
-        <v>-9.45356242177024</v>
+        <v>-15.15327067481331</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.54951859323778</v>
       </c>
       <c r="E48">
-        <v>-24.51837851374298</v>
+        <v>-32.57713764594295</v>
       </c>
       <c r="F48">
-        <v>0.6901574678645116</v>
+        <v>-2.896761193202045</v>
       </c>
       <c r="G48">
-        <v>-9.268019186248321</v>
+        <v>-15.94050627318763</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.59908637349486</v>
       </c>
       <c r="E49">
-        <v>-23.65384301246462</v>
+        <v>-32.18664280378754</v>
       </c>
       <c r="F49">
-        <v>0.8582572365472124</v>
+        <v>-3.008702622179356</v>
       </c>
       <c r="G49">
-        <v>-9.460403768721683</v>
+        <v>-15.51847719682263</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.66739640798015</v>
       </c>
       <c r="E50">
-        <v>-23.17472140550509</v>
+        <v>-31.8340444963653</v>
       </c>
       <c r="F50">
-        <v>0.8281063198201161</v>
+        <v>-2.780962885597299</v>
       </c>
       <c r="G50">
-        <v>-9.474398178672715</v>
+        <v>-16.10470516246536</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.75357991643368</v>
       </c>
       <c r="E51">
-        <v>-22.83599154973134</v>
+        <v>-30.77626768799463</v>
       </c>
       <c r="F51">
-        <v>0.7783943352433121</v>
+        <v>-2.852988602903313</v>
       </c>
       <c r="G51">
-        <v>-10.16733311003937</v>
+        <v>-16.07023428937261</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.85194001140381</v>
       </c>
       <c r="E52">
-        <v>-22.38272300088159</v>
+        <v>-31.2756587446125</v>
       </c>
       <c r="F52">
-        <v>0.6930120219345587</v>
+        <v>-2.748769214854899</v>
       </c>
       <c r="G52">
-        <v>-10.12882797503928</v>
+        <v>-15.93510374189</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.96382587442202</v>
       </c>
       <c r="E53">
-        <v>-21.82594712163852</v>
+        <v>-30.57478682244536</v>
       </c>
       <c r="F53">
-        <v>0.6590357045413341</v>
+        <v>-2.765923047032071</v>
       </c>
       <c r="G53">
-        <v>-10.230486781394</v>
+        <v>-16.15644018279313</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.08523002470767</v>
       </c>
       <c r="E54">
-        <v>-21.48812296066631</v>
+        <v>-29.11617440152276</v>
       </c>
       <c r="F54">
-        <v>0.7111955147934106</v>
+        <v>-3.236656077551335</v>
       </c>
       <c r="G54">
-        <v>-10.08834426343886</v>
+        <v>-16.80955584992514</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.20687924651434</v>
       </c>
       <c r="E55">
-        <v>-20.89816695236904</v>
+        <v>-30.44491924485339</v>
       </c>
       <c r="F55">
-        <v>0.4827864573498917</v>
+        <v>-3.130988703282827</v>
       </c>
       <c r="G55">
-        <v>-10.78324792774118</v>
+        <v>-16.60688299725214</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.3279869629188</v>
       </c>
       <c r="E56">
-        <v>-20.8366204621308</v>
+        <v>-29.75746292693398</v>
       </c>
       <c r="F56">
-        <v>0.5804857655708709</v>
+        <v>-3.290697110175169</v>
       </c>
       <c r="G56">
-        <v>-10.8010780856952</v>
+        <v>-15.82283838684438</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.44371342494575</v>
       </c>
       <c r="E57">
-        <v>-20.02980489055421</v>
+        <v>-29.14680499971064</v>
       </c>
       <c r="F57">
-        <v>0.5573635462565284</v>
+        <v>-2.958672544519877</v>
       </c>
       <c r="G57">
-        <v>-10.93780002563414</v>
+        <v>-15.88556057756395</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.54770127250645</v>
       </c>
       <c r="E58">
-        <v>-19.90058488474533</v>
+        <v>-29.04570228901539</v>
       </c>
       <c r="F58">
-        <v>0.7106777851666609</v>
+        <v>-2.993536871768902</v>
       </c>
       <c r="G58">
-        <v>-10.76363934770193</v>
+        <v>-16.80250942662623</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.64291547083121</v>
       </c>
       <c r="E59">
-        <v>-19.2081630950765</v>
+        <v>-28.30184156309343</v>
       </c>
       <c r="F59">
-        <v>0.6529463757633549</v>
+        <v>-2.884519579723473</v>
       </c>
       <c r="G59">
-        <v>-10.88099879921859</v>
+        <v>-16.74855301930272</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.72190001658836</v>
       </c>
       <c r="E60">
-        <v>-18.81081667174748</v>
+        <v>-27.98158335279698</v>
       </c>
       <c r="F60">
-        <v>0.6476183166285485</v>
+        <v>-3.319069522088455</v>
       </c>
       <c r="G60">
-        <v>-11.20626957362791</v>
+        <v>-15.8341881322185</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.78248460970424</v>
       </c>
       <c r="E61">
-        <v>-18.7749330437107</v>
+        <v>-28.21590471184987</v>
       </c>
       <c r="F61">
-        <v>0.2600450896763271</v>
+        <v>-3.294806640860457</v>
       </c>
       <c r="G61">
-        <v>-11.47414193929785</v>
+        <v>-16.45788108562697</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.82493040119673</v>
       </c>
       <c r="E62">
-        <v>-18.12953492813752</v>
+        <v>-28.01226829267295</v>
       </c>
       <c r="F62">
-        <v>0.4735037722341204</v>
+        <v>-3.159481228469519</v>
       </c>
       <c r="G62">
-        <v>-11.54282446898015</v>
+        <v>-16.97944765860851</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.84598219428897</v>
       </c>
       <c r="E63">
-        <v>-18.53633680519456</v>
+        <v>-27.10249333605797</v>
       </c>
       <c r="F63">
-        <v>0.2674457240529378</v>
+        <v>-3.044497206021725</v>
       </c>
       <c r="G63">
-        <v>-11.81192401151333</v>
+        <v>-17.24457036061164</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.8475388368549</v>
       </c>
       <c r="E64">
-        <v>-18.01241953335115</v>
+        <v>-26.87773158563527</v>
       </c>
       <c r="F64">
-        <v>0.4165435728828208</v>
+        <v>-3.149897845986531</v>
       </c>
       <c r="G64">
-        <v>-11.90717787338401</v>
+        <v>-17.07706071878043</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.83309329042356</v>
       </c>
       <c r="E65">
-        <v>-17.87913748635739</v>
+        <v>-27.49950465231043</v>
       </c>
       <c r="F65">
-        <v>0.3009879769270954</v>
+        <v>-3.274992920952896</v>
       </c>
       <c r="G65">
-        <v>-11.42404096730669</v>
+        <v>-16.8426338444659</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.79713643158107</v>
       </c>
       <c r="E66">
-        <v>-17.07916443900639</v>
+        <v>-26.88089698896663</v>
       </c>
       <c r="F66">
-        <v>0.1505755090289696</v>
+        <v>-3.286878336448263</v>
       </c>
       <c r="G66">
-        <v>-11.82572811061392</v>
+        <v>-16.39286368042658</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.74521174648669</v>
       </c>
       <c r="E67">
-        <v>-16.99268869935592</v>
+        <v>-26.96861805896921</v>
       </c>
       <c r="F67">
-        <v>0.120755939262993</v>
+        <v>-3.285960505365961</v>
       </c>
       <c r="G67">
-        <v>-11.30804650395876</v>
+        <v>-16.73941317664889</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.67892457205586</v>
       </c>
       <c r="E68">
-        <v>-17.6275807552313</v>
+        <v>-27.76112365268156</v>
       </c>
       <c r="F68">
-        <v>0.04289354523685344</v>
+        <v>-3.140237425335084</v>
       </c>
       <c r="G68">
-        <v>-12.18105159328618</v>
+        <v>-17.17566142664174</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.59617231201873</v>
       </c>
       <c r="E69">
-        <v>-16.72405509274691</v>
+        <v>-27.32465121392626</v>
       </c>
       <c r="F69">
-        <v>0.07003500318957925</v>
+        <v>-3.273671674945431</v>
       </c>
       <c r="G69">
-        <v>-11.89683218180708</v>
+        <v>-16.93600756638302</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.50535549203757</v>
       </c>
       <c r="E70">
-        <v>-17.06781608314317</v>
+        <v>-27.10412811517474</v>
       </c>
       <c r="F70">
-        <v>0.01829848868033333</v>
+        <v>-3.362171134790919</v>
       </c>
       <c r="G70">
-        <v>-11.65169211910097</v>
+        <v>-16.58283984627531</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.40621111027376</v>
       </c>
       <c r="E71">
-        <v>-16.87500271684458</v>
+        <v>-27.00768973270739</v>
       </c>
       <c r="F71">
-        <v>-0.2153649031991428</v>
+        <v>-3.552301334551073</v>
       </c>
       <c r="G71">
-        <v>-11.801611132152</v>
+        <v>-16.77307522862723</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.29746937542229</v>
       </c>
       <c r="E72">
-        <v>-16.7273563502985</v>
+        <v>-26.59870060270464</v>
       </c>
       <c r="F72">
-        <v>-0.02224678221709128</v>
+        <v>-3.888601932739616</v>
       </c>
       <c r="G72">
-        <v>-11.48121625298002</v>
+        <v>-16.55020809786663</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.18266855612823</v>
       </c>
       <c r="E73">
-        <v>-17.56177297095184</v>
+        <v>-27.33698677712316</v>
       </c>
       <c r="F73">
-        <v>-0.2953967914532142</v>
+        <v>-3.55122362856003</v>
       </c>
       <c r="G73">
-        <v>-11.17255174088305</v>
+        <v>-16.54934185537493</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.06126436980491</v>
       </c>
       <c r="E74">
-        <v>-17.63372136598571</v>
+        <v>-27.17308771736354</v>
       </c>
       <c r="F74">
-        <v>-0.3015258818665278</v>
+        <v>-3.587093593836054</v>
       </c>
       <c r="G74">
-        <v>-11.60914451913965</v>
+        <v>-16.7076804829475</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.9335775770897</v>
       </c>
       <c r="E75">
-        <v>-17.62115937908843</v>
+        <v>-26.09970352332544</v>
       </c>
       <c r="F75">
-        <v>-0.4160087420356279</v>
+        <v>-3.63982414922866</v>
       </c>
       <c r="G75">
-        <v>-11.25169480489686</v>
+        <v>-16.0597015681668</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.80558514210503</v>
       </c>
       <c r="E76">
-        <v>-18.32426383894135</v>
+        <v>-27.09116762256479</v>
       </c>
       <c r="F76">
-        <v>-0.3713365447374561</v>
+        <v>-4.21729231959864</v>
       </c>
       <c r="G76">
-        <v>-10.76520777160735</v>
+        <v>-15.88533417327634</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.67245275308855</v>
       </c>
       <c r="E77">
-        <v>-18.31860777490577</v>
+        <v>-27.88791639642232</v>
       </c>
       <c r="F77">
-        <v>-0.4290373045468585</v>
+        <v>-3.675266676924839</v>
       </c>
       <c r="G77">
-        <v>-10.87708430189818</v>
+        <v>-16.17105638422967</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.53548436957797</v>
       </c>
       <c r="E78">
-        <v>-18.26357323029055</v>
+        <v>-27.18069102522242</v>
       </c>
       <c r="F78">
-        <v>-0.3560606214624304</v>
+        <v>-4.049739273401787</v>
       </c>
       <c r="G78">
-        <v>-10.62023684066796</v>
+        <v>-15.41156515475124</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.39437768514198</v>
       </c>
       <c r="E79">
-        <v>-18.89374208777594</v>
+        <v>-29.48511144316466</v>
       </c>
       <c r="F79">
-        <v>-0.6016641010858587</v>
+        <v>-3.992359091777268</v>
       </c>
       <c r="G79">
-        <v>-10.18657091204239</v>
+        <v>-15.2286370528122</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.2442389164334</v>
       </c>
       <c r="E80">
-        <v>-19.41664498144163</v>
+        <v>-28.4096871715861</v>
       </c>
       <c r="F80">
-        <v>-0.4159689804002935</v>
+        <v>-4.122390408096915</v>
       </c>
       <c r="G80">
-        <v>-10.25829513411029</v>
+        <v>-15.74306696890194</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.08718097554259</v>
       </c>
       <c r="E81">
-        <v>-19.83115432125973</v>
+        <v>-28.42397903555431</v>
       </c>
       <c r="F81">
-        <v>-0.4893060033049393</v>
+        <v>-4.176230975809271</v>
       </c>
       <c r="G81">
-        <v>-9.965770950864238</v>
+        <v>-15.12221063153161</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.9217174442076</v>
       </c>
       <c r="E82">
-        <v>-20.24252542859051</v>
+        <v>-29.12950622900134</v>
       </c>
       <c r="F82">
-        <v>-0.663852127116226</v>
+        <v>-4.202715538411577</v>
       </c>
       <c r="G82">
-        <v>-9.677932352005071</v>
+        <v>-14.52282332682472</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.74156873837417</v>
       </c>
       <c r="E83">
-        <v>-20.55568299164294</v>
+        <v>-29.86369413444291</v>
       </c>
       <c r="F83">
-        <v>-0.631947556597403</v>
+        <v>-4.194046673541281</v>
       </c>
       <c r="G83">
-        <v>-9.568664392854002</v>
+        <v>-14.6257716532523</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.54663448702602</v>
       </c>
       <c r="E84">
-        <v>-21.90682113894151</v>
+        <v>-30.85276719940621</v>
       </c>
       <c r="F84">
-        <v>-0.491550878966526</v>
+        <v>-4.015097776984114</v>
       </c>
       <c r="G84">
-        <v>-9.056993984095753</v>
+        <v>-13.79423956382548</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.33475999798274</v>
       </c>
       <c r="E85">
-        <v>-23.26491049384185</v>
+        <v>-32.21563635862164</v>
       </c>
       <c r="F85">
-        <v>-0.7109506125371975</v>
+        <v>-4.307103913410162</v>
       </c>
       <c r="G85">
-        <v>-8.821021654426726</v>
+        <v>-13.72461368294485</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.10149622817563</v>
       </c>
       <c r="E86">
-        <v>-23.71918889239531</v>
+        <v>-31.85856844735384</v>
       </c>
       <c r="F86">
-        <v>-0.8058367850582696</v>
+        <v>-4.201350388931764</v>
       </c>
       <c r="G86">
-        <v>-8.662253186829874</v>
+        <v>-13.70519213253449</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.853970168486205</v>
       </c>
       <c r="E87">
-        <v>-25.02836167106479</v>
+        <v>-32.90631242156051</v>
       </c>
       <c r="F87">
-        <v>-0.7155132601918172</v>
+        <v>-4.353284567748832</v>
       </c>
       <c r="G87">
-        <v>-8.428945209067118</v>
+        <v>-14.40789197926205</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.591200457218523</v>
       </c>
       <c r="E88">
-        <v>-25.66309975882392</v>
+        <v>-33.94305899663956</v>
       </c>
       <c r="F88">
-        <v>-0.592172667384582</v>
+        <v>-4.280788337758028</v>
       </c>
       <c r="G88">
-        <v>-8.480768822376987</v>
+        <v>-13.40013368293136</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.315115324700834</v>
       </c>
       <c r="E89">
-        <v>-27.56317499685828</v>
+        <v>-35.53065367848564</v>
       </c>
       <c r="F89">
-        <v>-0.9858410216866021</v>
+        <v>-4.418366909484581</v>
       </c>
       <c r="G89">
-        <v>-7.869250841564835</v>
+        <v>-13.61044357878397</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.029736752311651</v>
       </c>
       <c r="E90">
-        <v>-28.20448390040253</v>
+        <v>-37.40196631386029</v>
       </c>
       <c r="F90">
-        <v>-0.9629084985075007</v>
+        <v>-4.641651686174382</v>
       </c>
       <c r="G90">
-        <v>-7.876052813857564</v>
+        <v>-13.57154141597519</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.736266519902571</v>
       </c>
       <c r="E91">
-        <v>-30.12803927616666</v>
+        <v>-37.37704385715907</v>
       </c>
       <c r="F91">
-        <v>-0.97546323486433</v>
+        <v>-4.916071582638996</v>
       </c>
       <c r="G91">
-        <v>-7.940925845309345</v>
+        <v>-13.3497570883292</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.439536855648166</v>
       </c>
       <c r="E92">
-        <v>-31.45815624712162</v>
+        <v>-38.23092612333438</v>
       </c>
       <c r="F92">
-        <v>-0.965729089514033</v>
+        <v>-4.745323523369546</v>
       </c>
       <c r="G92">
-        <v>-8.052628470857522</v>
+        <v>-13.30538512918083</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.146137026126549</v>
       </c>
       <c r="E93">
-        <v>-33.40763940081666</v>
+        <v>-39.93298024996133</v>
       </c>
       <c r="F93">
-        <v>-1.194912670479169</v>
+        <v>-4.798514651038108</v>
       </c>
       <c r="G93">
-        <v>-7.820386890101584</v>
+        <v>-13.53486064016216</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.855287927728122</v>
       </c>
       <c r="E94">
-        <v>-34.89800321724405</v>
+        <v>-41.556347612231</v>
       </c>
       <c r="F94">
-        <v>-1.426875424080698</v>
+        <v>-5.021690083230739</v>
       </c>
       <c r="G94">
-        <v>-8.073556101963661</v>
+        <v>-13.34911725012511</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.571459745702879</v>
       </c>
       <c r="E95">
-        <v>-36.57249478682332</v>
+        <v>-43.4941156036682</v>
       </c>
       <c r="F95">
-        <v>-1.459740900786769</v>
+        <v>-4.872630339301385</v>
       </c>
       <c r="G95">
-        <v>-8.487669231316499</v>
+        <v>-14.03413787509039</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.296964725861558</v>
       </c>
       <c r="E96">
-        <v>-38.0427793495007</v>
+        <v>-44.61957724879451</v>
       </c>
       <c r="F96">
-        <v>-1.548753948421992</v>
+        <v>-5.051242090325611</v>
       </c>
       <c r="G96">
-        <v>-8.486579865758763</v>
+        <v>-14.06681884182245</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.03102239849239</v>
       </c>
       <c r="E97">
-        <v>-40.41735715100677</v>
+        <v>-46.12469256930189</v>
       </c>
       <c r="F97">
-        <v>-1.465183274623161</v>
+        <v>-5.085161250368043</v>
       </c>
       <c r="G97">
-        <v>-8.901129397579009</v>
+        <v>-14.06154755938721</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.780956863462624</v>
       </c>
       <c r="E98">
-        <v>-42.13860521471523</v>
+        <v>-47.44572768563447</v>
       </c>
       <c r="F98">
-        <v>-1.554263420018012</v>
+        <v>-5.240219202661068</v>
       </c>
       <c r="G98">
-        <v>-8.768866637739352</v>
+        <v>-14.0191443331745</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.54931659649065</v>
       </c>
       <c r="E99">
-        <v>-44.46007080882234</v>
+        <v>-48.74913118841818</v>
       </c>
       <c r="F99">
-        <v>-1.694895353991284</v>
+        <v>-5.521437510400458</v>
       </c>
       <c r="G99">
-        <v>-8.990952837768809</v>
+        <v>-14.59313990484362</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.337561181636907</v>
       </c>
       <c r="E100">
-        <v>-46.48506400235829</v>
+        <v>-49.6469475772974</v>
       </c>
       <c r="F100">
-        <v>-1.899306607775701</v>
+        <v>-5.599130089109024</v>
       </c>
       <c r="G100">
-        <v>-8.993085631782447</v>
+        <v>-15.2523996593457</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.150089721914092</v>
       </c>
       <c r="E101">
-        <v>-48.24145755284028</v>
+        <v>-50.92962085819251</v>
       </c>
       <c r="F101">
-        <v>-2.079278538075324</v>
+        <v>-5.551847706124631</v>
       </c>
       <c r="G101">
-        <v>-9.093835539765196</v>
+        <v>-14.8238819673469</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.988923782143544</v>
       </c>
       <c r="E102">
-        <v>-50.54824749480704</v>
+        <v>-53.20589454594008</v>
       </c>
       <c r="F102">
-        <v>-2.273169525844188</v>
+        <v>-5.554914322249795</v>
       </c>
       <c r="G102">
-        <v>-9.693836432903698</v>
+        <v>-15.5880112034996</v>
       </c>
     </row>
   </sheetData>
